--- a/daily_matches/job_matches_2026-06-03.xlsx
+++ b/daily_matches/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Technical Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Softchoice</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Pinecone, BigQuery</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2514cb3d6eaca2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6b03669fcb256f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>AI Engineer, Data Scientist, RAG, Cortex, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
+          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Scientist - Airvoyant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Data Scientist, XGBoost, Redshift, Docker, Git, Redshift, Hadoop, Tableau, Power BI, Quicksight</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,159 +566,159 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fe2b1f52651159</t>
+          <t>https://www.indeed.com/viewjob?jk=f54bacadbab2a4ac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Senior Engineer, AI Data Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>AI Engineer, RAG, S3, Apache Airflow, CI/CD, Git, Kafka, Hadoop, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8642e77f775f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae6b623863032dc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Software Engineer AI/ML</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, MLflow, FastAPI, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ff77dccb34c1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4c50522f01638f</t>
+          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bennett Family of Companies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McDonough, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77baab252900263</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce5cf18206c40a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
+          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>AI / ML Engineer – Healthcare AI Systems</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, BigQuery, Dataflow, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff84a48bf7f2b214</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd6ee1a78b614e0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Senior Cloud Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a341fbae4ab3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL</t>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d370271ca54d590</t>
+          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL</t>
+          <t>RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dc0480a620e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Customer Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8f514248ec1f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9bc56102b3216b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Applied Researcher 1</t>
+          <t>Windows System Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Allthenticate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, LLaMA, Hugging Face, PyTorch, OpenCV, MLflow, Docker, Git</t>
+          <t>RAG, TensorFlow, PyTorch, MySQL, MongoDB, Tableau, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dae6a19b7149d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fe708f5a8d8f06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer/Developer - Onsite</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CertiK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, Apache Airflow, CI/CD, Git, Databricks, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092856cce449bac1</t>
+          <t>https://www.indeed.com/viewjob?jk=165a77cf906f8072</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II, Machine Learning</t>
+          <t>Software Engineer - Connected Consumer and Vehicle Applications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Redshift, Kinesis, MLflow, Docker, Kubernetes, Git, Redshift</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7b943dfe02fe0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ee7590b8ddcee3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II, Machine Learning</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Redshift, Kinesis, MLflow, Docker, Kubernetes, Git, Redshift</t>
+          <t>Data Scientist, RAG, MLflow, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a85d9436e5d287</t>
+          <t>https://www.indeed.com/viewjob?jk=ae252d8f4e554400</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Analyst IV</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Lasting Change Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redmond, OR, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>RAG, Synapse, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Developer Infrastructure</t>
+          <t>Software Engineer II, Machine Learning</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, Python</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21cc7ed57f56baa</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d9c5abf283510f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Konexus, Inc.</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01891cd9bc4d364f</t>
+          <t>https://www.indeed.com/viewjob?jk=eca6f84ddd9acb27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Software Engineer, Workflow Platforms</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
+          <t>https://www.indeed.com/viewjob?jk=a42266278de6e979</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>AAA Life Insurance Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
+          <t>https://www.indeed.com/viewjob?jk=dec9ae3c3ef177d1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Growth</t>
+          <t>Process Development Engineer III, AI and Data Science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Git, Databricks, NoSQL, Python, SQL, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e646f19a514d4d01</t>
+          <t>https://www.indeed.com/viewjob?jk=4239ce14bf01c32f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Software Engineer, Early Career</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1ddbe726c249e4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Software Engineer, Early Career</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
+          <t>https://www.indeed.com/viewjob?jk=019f2e15f68beb04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, AI Developer Productivity - Summer 2026</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HYPERPROOF</t>
+          <t>Belvedere Trading</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Kinesis, BigQuery, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce755e263286decc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2c89a549df7ec7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Ceresti Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, Copilot, S3, Data Lake, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324835225383dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hagerty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, XGBoost, FastAPI, Docker, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,137 +1441,137 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b540737ddca3258</t>
+          <t>https://www.indeed.com/viewjob?jk=88275a07e7d1bcde</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lions Path Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, Gemini, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e135a5b41eaec3</t>
+          <t>https://www.indeed.com/viewjob?jk=39455c2f7a371c22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Notified</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f1c84f0358d87e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4278b628e3cf21c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67830fd25321947</t>
+          <t>https://www.indeed.com/viewjob?jk=24ae78ac82d6881b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Notified</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, GitHub Actions, Git, Tableau, MicroStrategy, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57ff87e9fa89ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b2454f6a69c949</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Senior Software Engineer - Employment Compliance Solutions</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Franklin Electric</t>
+          <t>Bankers Financial Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Docker, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e39ad5280a53f2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7460ebc4e8958b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Sr Full Stack BI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, PostgreSQL, Tableau, Power BI, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=424506ecdf827110</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Channel Processing</t>
+          <t>Senior Data Solution Architect/Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Land O'Lakes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, EC2, Jenkins, Terraform, Git, MySQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Data Lake, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3843bd566fb5361</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbfa69a27310b8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer (contract)</t>
+          <t>Senior Associate, Software Engineering - Development</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Glue, Data Lake, Apache Airflow, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09530a3bb367b138</t>
+          <t>https://www.indeed.com/viewjob?jk=5540a18b7e5f9c66</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Architect - Business Applications</t>
+          <t>Senior Data Engineer – Healthcare Data Platforms</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Tableau, Python, SQL, R, Java, Scala, A/B Testing</t>
+          <t>BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,322 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb6ff3f717fe05b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Docker, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85782b7bf2c97f5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior AI Programmer Analyst</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>University of New England</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Portland, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a48dba940b9138f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Specialty Software Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24d67015783cf3d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Data Solutions Engineer II</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Axon</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0c2aeb93b4b7b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Copart, Inc</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3349a53751a5d0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Innovative Systems</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Mitchell, SD, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6be6b123a817d3f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ERP Suites</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>LangChain, MLflow, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1caae7d1c946061</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Technical Training EngineerNew</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Zscaler</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Data Lake, Git, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaa171f7a0b8410</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Technical Training Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Zscaler</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Data Lake, Git, R</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=125483e11f7273a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-03.xlsx
+++ b/daily_matches/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6b03669fcb256f</t>
+          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Cortex, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, MLflow, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=22e1934f3e6e801c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist - Airvoyant</t>
+          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>McKinney</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, Redshift, Docker, Git, Redshift, Hadoop, Tableau, Power BI, Quicksight</t>
+          <t>RAG, Gemini, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git, BigQuery, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f54bacadbab2a4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI Data Management</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Apache Airflow, CI/CD, Git, Kafka, Hadoop, MongoDB, Cassandra</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae6b623863032dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Evendale, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, MLflow, FastAPI, CI/CD, Git, Databricks, Python</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
+          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
+          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer Intern, AI Developer Productivity - Summer 2026New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bennett Family of Companies</t>
+          <t>HYPERPROOF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McDonough, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Databricks</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce5cf18206c40a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9eaff470e1efda6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Data Engineer - Senior Consultant level</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Kafka, Hadoop, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0ad776b6fe898e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI / ML Engineer – Healthcare AI Systems</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, BigQuery, Dataflow, CI/CD, Terraform, BigQuery</t>
+          <t>RAG, Pinecone, FastAPI, CI/CD, GitHub Actions, Git, Databricks, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd6ee1a78b614e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer (Remote US)</t>
+          <t>AI / GenAI / LLM Engineer Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Diagonal Matrix Ltd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,46 +797,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
+          <t>https://www.indeed.com/viewjob?jk=ca2ffcf8ed29469a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Kastle Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec39517acd900e19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Performance Pacing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, CI/CD, Git, PySpark, Kafka, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
+          <t>https://www.indeed.com/viewjob?jk=57cad4feed5a9a95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Customer Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Sightly Enterprises, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9bc56102b3216b</t>
+          <t>https://www.indeed.com/viewjob?jk=17dc442b6e31405d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Windows System Administrator</t>
+          <t>Software Engineer, Early Career</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allthenticate</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MySQL, MongoDB, Tableau, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fe708f5a8d8f06</t>
+          <t>https://www.indeed.com/viewjob?jk=346a896d2a1d32de</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer, Early Career</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CertiK</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Apache Airflow, CI/CD, Git, Databricks, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165a77cf906f8072</t>
+          <t>https://www.indeed.com/viewjob?jk=d5377eca8f57f142</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer - Connected Consumer and Vehicle Applications</t>
+          <t>Data Scientist, Senior Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ee7590b8ddcee3</t>
+          <t>https://www.indeed.com/viewjob?jk=434c3357f5cb3f8e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Software Engineer Senior- AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae252d8f4e554400</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6af4a3c8b51e46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lasting Change Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b04ad1f767243b7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II, Machine Learning</t>
+          <t>MCP Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Sightly Enterprises, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d9c5abf283510f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaef8d00c5f11e1e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca6f84ddd9acb27</t>
+          <t>https://www.indeed.com/viewjob?jk=bb53c29e352fcf59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Workflow Platforms</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42266278de6e979</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2d137d1580a637</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AAA Life Insurance Company</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, NoSQL, SQL, R, Java</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec9ae3c3ef177d1</t>
+          <t>https://www.indeed.com/viewjob?jk=158092feafd1ca75</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Process Development Engineer III, AI and Data Science</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, NoSQL, Python, SQL, R, Optimization, Bayesian</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4239ce14bf01c32f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c90219bfe55d6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1ddbe726c249e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b79121be6349092</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019f2e15f68beb04</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbf1615514e6cc1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Belvedere Trading</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lubbock, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, BigQuery, Kafka, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,392 +1371,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2c89a549df7ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e5454d55539edf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ceresti Health</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Data Lake, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Scientist III</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Hagerty</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, XGBoost, FastAPI, Docker, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88275a07e7d1bcde</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AI Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Lions Path Consulting</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Franklin, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39455c2f7a371c22</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Notified</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Woburn, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4278b628e3cf21c</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Foot Locker</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ae78ac82d6881b</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Notified</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Woburn, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b2454f6a69c949</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Employment Compliance Solutions</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bankers Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7460ebc4e8958b</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr Full Stack BI Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>McLane Company</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Temple, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, PostgreSQL, Tableau, Power BI, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=424506ecdf827110</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Solution Architect/Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Land O'Lakes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Arden Hills, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, Data Lake, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbfa69a27310b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Associate, Software Engineering - Development</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Kyndryl</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5540a18b7e5f9c66</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Healthcare Data Platforms</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Expleo Group</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=62b689fab0b7e50e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-03.xlsx
+++ b/daily_matches/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
+          <t>Gemini, Cortex, Redshift, BigQuery, AKS, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, MLflow, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e1934f3e6e801c</t>
+          <t>https://www.indeed.com/viewjob?jk=252de2ad1a0af01a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
+          <t>Senior Software Engineer, ML Platform | Parafin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>McKinney</t>
+          <t>carnaby fox</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git, BigQuery, MongoDB</t>
+          <t>Data Scientist, Machine Learning Engineer, Kinesis, MLflow, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
+          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Machine Learning Engineer, RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Machine Learning Engineer, RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Application Architect — AI/ML Ops &amp; Data Solutions</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Great American Insurance Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
+          <t>Generative AI, RAG, Cortex, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=e837ad77e0c2d0d0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, AI Developer Productivity - Summer 2026New</t>
+          <t>Sr Product Software Engineer - Ad Decisioning Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HYPERPROOF</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, Kinesis, Docker, Kubernetes, AKS, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9eaff470e1efda6</t>
+          <t>https://www.indeed.com/viewjob?jk=a657943a44b7d335</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Consultant level</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Kafka, Hadoop, NoSQL, SQL, R</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0ad776b6fe898e</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1b5426a6197ba8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, FastAPI, CI/CD, GitHub Actions, Git, Databricks, Kafka, Power BI, Python</t>
+          <t>Data Scientist, Synapse, Data Lake, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI / GenAI / LLM Engineer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diagonal Matrix Ltd</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca2ffcf8ed29469a</t>
+          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kastle Systems</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec39517acd900e19</t>
+          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Performance Pacing</t>
+          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PySpark, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, S3, Docker, CI/CD, Git, Snowflake, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57cad4feed5a9a95</t>
+          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sightly Enterprises, Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Glue, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17dc442b6e31405d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>MacDonald-Miller Facility Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346a896d2a1d32de</t>
+          <t>https://www.indeed.com/viewjob?jk=a8c7606a057c5d2d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career</t>
+          <t>Data Scientist II - Commercial Insights &amp; Analytics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5377eca8f57f142</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbdf3d12ea99545</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior Associate</t>
+          <t>Senior Software Engineer, AI Platform &amp; Agents</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Coalition Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Docker, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=434c3357f5cb3f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b12380541a994fe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer Senior- AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+          <t>RAG, Data Lake, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6af4a3c8b51e46</t>
+          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior AI Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ScienceLogic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b04ad1f767243b7</t>
+          <t>https://www.indeed.com/viewjob?jk=766fd2b94c89ad1f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MCP Solutions Architect</t>
+          <t>Senior Solution Architect (f/m/d)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sightly Enterprises, Inc.</t>
+          <t>adjoe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, Snowflake, Python, SQL, R</t>
+          <t>RAG, Data Lake, Tableau, Quicksight, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaef8d00c5f11e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5ee59a94c06bfb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Sr. Software Engineer II (DevOps)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Hi Marley</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Redshift, CI/CD, Terraform, Redshift, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb53c29e352fcf59</t>
+          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>NCD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, AKS, BigQuery, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2d137d1580a637</t>
+          <t>https://www.indeed.com/viewjob?jk=873e198c2c9ffb65</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Senior Software Engineer: $150-170,000, 5+ Years Required, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Terraform, MongoDB, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158092feafd1ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=95162020aafe7ef1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>GenAI Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Niskayuna, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c90219bfe55d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2f010ad130e8bd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Cloud Engineer Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Diagonal Matrix Ltd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b79121be6349092</t>
+          <t>https://www.indeed.com/viewjob?jk=3a13a04cde1ab2a3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Software Engineer II - Ad Platform, Salesforce CRM Analytics</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Snowflake, Databricks, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbf1615514e6cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=385d226a9a1ff855</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lubbock, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e5454d55539edf</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed67476a36487a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Scientist 1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Daikin/Goodman Manufacturing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Waller, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,52 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b689fab0b7e50e</t>
+          <t>https://www.indeed.com/viewjob?jk=05b9216a4048b8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AXCE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Gemini, Copilot, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16837e7c57a46cfd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-03.xlsx
+++ b/daily_matches/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gemini, Cortex, Redshift, BigQuery, AKS, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, S3, Data Lake, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfe18dbf4b291f3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252de2ad1a0af01a</t>
+          <t>https://www.indeed.com/viewjob?jk=34430b584944faaf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Platform | Parafin</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>carnaby fox</t>
+          <t>Artisan Studios, LLC DBA Amy Howard At Home &amp; A Makers' Studio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Kinesis, MLflow, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, PyTorch, S3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
+          <t>https://www.indeed.com/viewjob?jk=7350027af6d67644</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, MLflow, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
+          <t>https://www.indeed.com/viewjob?jk=14d57e3def97a538</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Full Stack Engineer Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+          <t>LangChain, RAG, LLaMA, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
+          <t>https://www.indeed.com/viewjob?jk=40580437979bb471</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Application Architect — AI/ML Ops &amp; Data Solutions</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Databricks, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e837ad77e0c2d0d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer - Ad Decisioning Engineering</t>
+          <t>Distinguished Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Kinesis, Docker, Kubernetes, AKS, Terraform, Git, Kafka</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a657943a44b7d335</t>
+          <t>https://www.indeed.com/viewjob?jk=8aba53f094844bbe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software engineer, generative AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1b5426a6197ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=f032e73559e166a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software engineer, generative AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, Data Lake, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f63f571f2aa7d9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software engineer, generative AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4887c446f87c2c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, EC2, FastAPI, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=720a7471405c4ce4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Docker, CI/CD, Git, Snowflake, Databricks, Python, R, Java</t>
+          <t>AI Engineer, RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+          <t>https://www.indeed.com/viewjob?jk=47eb49ae40d3103f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Glue, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
+          <t>https://www.indeed.com/viewjob?jk=837b89c39e0b1f1d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MacDonald-Miller Facility Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c7606a057c5d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=101a2c6e0c8a3069</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist II - Commercial Insights &amp; Analytics</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbdf3d12ea99545</t>
+          <t>https://www.indeed.com/viewjob?jk=95364f39594f2d52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Platform &amp; Agents</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coalition Inc.</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Docker, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b12380541a994fe</t>
+          <t>https://www.indeed.com/viewjob?jk=82c698a308ef14f8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL/ELT Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, S3, Glue, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,137 +1056,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c2c00b592047da</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Platform Integration Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ScienceLogic</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Glue, Athena, Jenkins, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766fd2b94c89ad1f</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Solution Architect (f/m/d)</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>adjoe</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Tableau, Quicksight, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5ee59a94c06bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=a988b9cc3e868674</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II (DevOps)</t>
+          <t>Full Stack Data Scientist (AI/ML)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hi Marley</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, CI/CD, Terraform, Redshift, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, AWS SageMaker, S3, Redshift, MLflow, CI/CD, Redshift, PySpark, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd357490d7d7ae24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Operations Engineer</t>
+          <t>Sr. DevOps Engineer - AI and Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NCD</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, AKS, BigQuery, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, AWS SageMaker, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=873e198c2c9ffb65</t>
+          <t>https://www.indeed.com/viewjob?jk=4af551425106ee82</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer: $150-170,000, 5+ Years Required, MN Based, Hybrid - 2 Days in Office</t>
+          <t>AI/Machine Learning Engineer - Python - Loops</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95162020aafe7ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac138adc8a63a27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GenAI Engineer II</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Tunnl</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Niskayuna, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, PyTorch, Git, Python, R, Scala</t>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2f010ad130e8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Engineer Intern</t>
+          <t>Senior Associate Engineer, Product Software</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diagonal Matrix Ltd</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, S3, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a13a04cde1ab2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e07b286e6c9ce7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II - Ad Platform, Salesforce CRM Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, Kafka, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Dataflow, CI/CD, Git, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385d226a9a1ff855</t>
+          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Engineer - Automated Chromatography Analysis (EFT)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,77 +1371,1267 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed67476a36487a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3290f296dc2085d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist 1</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Daikin/Goodman Manufacturing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Waller, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Java, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, ChromaDB, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b9216a4048b8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=56fecfae6dbcd703</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AXCE</t>
+          <t>Sundays For Dogs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f88f0427926d7cef</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Java Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Snowflake, Databricks, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3119c9bcbe4438d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, Apache Airflow, CI/CD, Git, Snowflake, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d648d27c45edb008</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Java Architect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Snowflake, Databricks, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=396ec5e9883f5f9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Java Architect</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Snowflake, Databricks, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d99ab1f9a08e8816</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PHP Developer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>S3, EC2, CI/CD, Git, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=052fe054883f9804</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Java Architect</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Snowflake, Databricks, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdd8159ee450ee84</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Java Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Snowflake, Databricks, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd5bb74c926a79da</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Java Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Snowflake, Databricks, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11916b503bd40fc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AWS Developer / Administrator</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a3c84e2687fbb09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CNA Insurance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d7dbabe92f62957</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Engineer/Sr Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cdf35c48d37a3b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Engineer â€“ Python/AI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, MLflow, Docker, CI/CD, Jenkins, Git, MongoDB, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Test Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeec795671c13c81</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Digital Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AFL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Duncan, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85bed9161c5e49a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Buyer success Analyst</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Tableau, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22fb6eea67cf158a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Walker &amp; Dunlop</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3dadc30dce5db5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mgr, Customer Success Engineering</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>10</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, Gemini, Copilot, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16837e7c57a46cfd</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Cortex, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c921ac3aca8a45d</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75317bd61a4e5ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Snowflake Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, S3, Snowflake, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (AWS / DevOps) (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Aeroflow Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99996c1b7c953ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hollstadt Consulting</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Content Management System</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Docker, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55ea64139a3ba68d</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Home Loans Loss Forecasting Analytics, Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b76220729eedfef</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Service Experts</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Databricks, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=498072db4d3d2153</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Advisor - Antibody Developability Validation &amp; Benchmarking</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, PyTorch, MLflow, R, Scala, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1422a48b1397346b</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>skyline career</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=855edc77ab853d90</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Downers Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f9f81c63d5f07a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f20584980bbeadf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=968762cf0c573d67</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9d6d6e8fd68b928</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c42dcfafc3094053</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=286e3a5f3e0486c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2728de4abc2aee14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d21e7b61832b91</t>
         </is>
       </c>
     </row>
